--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Syracuse_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Syracuse_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Lid - Deli (6/32oz)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
@@ -477,20 +471,14 @@
           <t>Container - Deli (8oz)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -500,20 +488,14 @@
           <t>Container - Deli (32oz)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="5">
@@ -527,20 +509,14 @@
           <t>Container - Deli (16oz)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2.73</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2.73</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.73</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +530,14 @@
           <t>Vita Coco - Coconut Water 500ml</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>23.93</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>23.93</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23.93</v>
       </c>
     </row>
     <row r="7">
@@ -581,20 +551,14 @@
           <t>Kilogram Chai Concentrate</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>86.10</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>344.40</t>
-        </is>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>344.4</v>
       </c>
     </row>
     <row r="8">
@@ -604,20 +568,14 @@
           <t>Fiji Water 1L</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="9">
@@ -627,20 +585,14 @@
           <t>Fiji Water 500ml</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>18.50</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>18.50</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>18.5</v>
       </c>
     </row>
     <row r="10">
@@ -650,20 +602,14 @@
           <t>Register Tape - Thermal (3.125" x 230')</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>49.99</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>49.99</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="E10" t="n">
+        <v>49.99</v>
       </c>
     </row>
     <row r="11">
@@ -677,20 +623,14 @@
           <t>Matcha - Jade Leaf</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>44.07</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>132.21</t>
-        </is>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>132.21</v>
       </c>
     </row>
     <row r="12">
@@ -700,20 +640,14 @@
           <t>Urnex - Cafiza</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>9.39</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>18.78</t>
-        </is>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>18.78</v>
       </c>
     </row>
     <row r="13">
@@ -727,20 +661,14 @@
           <t>Maple Syrup (pure)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>84.00</t>
-        </is>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>42</v>
+      </c>
+      <c r="E13" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="14">
@@ -754,20 +682,14 @@
           <t>Torani - Pumpkin Pie Sauce</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>17.40</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>34.80</t>
-        </is>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>34.8</v>
       </c>
     </row>
     <row r="15">
@@ -781,20 +703,14 @@
           <t>Torani - Dark Chocolate Sauce</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -808,20 +724,14 @@
           <t>Torani - Caramel Sauce</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>17.50</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -835,20 +745,14 @@
           <t>Supplement - Collagen</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>33.99</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>33.99</t>
-        </is>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="E17" t="n">
+        <v>33.99</v>
       </c>
     </row>
     <row r="18">
@@ -862,20 +766,14 @@
           <t>Lid Espresso - 4oz</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="19">
@@ -889,20 +787,14 @@
           <t>FRZ Fruit - Mango</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
